--- a/survey_templates/047_it_tech_resources_satisfaction_employment_survey--survey_templates.xlsx
+++ b/survey_templates/047_it_tech_resources_satisfaction_employment_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -538,12 +538,12 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>category_id</t>
+          <t>category</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -561,17 +561,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>description_id</t>
+          <t>assigned_tool</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Assigned Tool</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -584,17 +584,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>assigned_tool</t>
+          <t>tool_used</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Assigned Tool</t>
+          <t>Tool Used</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>assigned_tool_id</t>
+          <t>tool_used_duration</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Tool</t>
+          <t>Tool Used Duration</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>assigned_tool_name</t>
+          <t>tool_used_frequency</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tool Name</t>
+          <t>Tool Used Frequency</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -653,17 +653,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>assigned_tool_2</t>
+          <t>satisfaction</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Tool 2</t>
+          <t>Satisfaction</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>assigned_tool_2_id</t>
+          <t>team_members</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Tool 2</t>
+          <t>Team Members</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>assigned_tool_3</t>
+          <t>support_frequency</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tool 3</t>
+          <t>Support Frequency</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>assigned_tool_3_id</t>
+          <t>support_duration</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Tool 3</t>
+          <t>Support Duration</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>assigned_tool_4</t>
+          <t>overall_satisfaction</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Tool 4</t>
+          <t>Overall Satisfaction</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -768,159 +768,21 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>assigned_tool_4_id</t>
+          <t>notes</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tool 4</t>
+          <t>Notes</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>assigned_tool_5</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Tool 5</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>assigned_tool_5_id</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Tool 5</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>form_id</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Form Id</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>category_id</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Category</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>description</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Description</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>assigned_tool_2</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Tool 2</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -937,12 +799,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="28" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -970,12 +832,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -987,284 +849,505 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>category_id_choices</t>
+          <t>it_tech_resources_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>neither_satisfied_nor_dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Neither Satisfied Nor Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>category_id_choices</t>
+          <t>it_tech_resources_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>description_id_choices</t>
+          <t>it_tech_resources_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>description_id_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>category_1</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Category 1</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>assigned_tool_id_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>category_2</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Category 2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>assigned_tool_id_choices</t>
+          <t>category_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>category_3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Category 3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>assigned_tool_2_id_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>assigned_tool_2_id_choices</t>
+          <t>assigned_tool_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>assigned_tool_3_id_choices</t>
+          <t>tool_used_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tool_1</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tool 1</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>assigned_tool_3_id_choices</t>
+          <t>tool_used_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>tool_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Tool 2</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>assigned_tool_4_id_choices</t>
+          <t>tool_used_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>tool_3</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Tool 3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>assigned_tool_4_id_choices</t>
+          <t>tool_used_frequency_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>assigned_tool_5_id_choices</t>
+          <t>tool_used_frequency_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>assigned_tool_5_id_choices</t>
+          <t>tool_used_frequency_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>monthly</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Monthly</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>category_id_choices</t>
+          <t>tool_used_frequency_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>category_id_choices</t>
+          <t>satisfaction_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>neither_satisfied_nor_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Neither Satisfied Nor Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Somewhat Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Very Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>support_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Daily</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>support_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Weekly</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>support_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Monthly</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>support_frequency_choices</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>rarely</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Rarely</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>very_satisfied</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Very Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>somewhat_satisfied</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Somewhat Satisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>neither_satisfied_nor_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Neither Satisfied Nor Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>somewhat_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Somewhat Dissatisfied</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>overall_satisfaction_choices</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>very_dissatisfied</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
